--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
@@ -286,12 +286,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/20 19:49:17</t>
+          <t>08/27 10:05:01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -301,7 +301,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -313,12 +313,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/20 18:15:36</t>
+          <t>08/20 19:49:17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -328,7 +328,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -340,83 +340,110 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>08/20 18:15:36</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>08/19 13:51:31</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>8333</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>180000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>180000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14285</t>
+          <t>21428.57</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>14573</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>7143.57</t>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>6855.57</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/27 09:56:58</t>
+          <t>08/27 14:01:57</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7142.86</t>
+          <t>21818.18</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/20 18:15:31</t>
+          <t>08/27 09:56:58</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>7142.86</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,166 +159,181 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>08/20 18:15:31</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>5952.38</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>08/19 12:21:27</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>70000</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>8333.33</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/27 10:05:01</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/20 19:49:17</t>
+          <t>08/27 10:05:01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -328,7 +343,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -340,12 +355,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/20 18:15:36</t>
+          <t>08/20 19:49:17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -355,7 +370,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -367,83 +382,110 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>08/20 18:15:36</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>08/19 13:51:31</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>8333</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>180000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>360000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14573</t>
+          <t>43246.75</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>14573</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>6855.57</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>28673.75</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
@@ -328,12 +328,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/27 10:05:01</t>
+          <t>08/27 15:15:22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -343,7 +343,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -355,12 +355,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/20 19:49:17</t>
+          <t>08/27 10:05:01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -370,7 +370,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -382,12 +382,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/20 18:15:36</t>
+          <t>08/20 19:49:17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -397,7 +397,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -409,83 +409,110 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>08/20 18:15:36</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>08/19 13:51:31</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>8333</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>360000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>43246.75</t>
+          <t>360000</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14573</t>
+          <t>43246.75</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>43246</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>28673.75</t>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0.75</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/27 14:01:57</t>
+          <t>09/01 10:16:07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21818.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/27 09:56:58</t>
+          <t>08/27 14:01:57</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7142.86</t>
+          <t>21818.18</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/20 18:15:31</t>
+          <t>08/27 09:56:58</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>7142.86</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,166 +201,181 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>08/20 18:15:31</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5952.38</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>08/19 12:21:27</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>70000</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>8333.33</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/27 15:15:22</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>28673</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/27 10:05:01</t>
+          <t>08/27 15:15:22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -370,7 +385,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -382,12 +397,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/20 19:49:17</t>
+          <t>08/27 10:05:01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -397,7 +412,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -409,12 +424,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/20 18:15:36</t>
+          <t>08/20 19:49:17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -424,7 +439,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -436,83 +451,110 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>08/20 18:15:36</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>08/19 13:51:31</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>8333</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>360000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>43246.75</t>
+          <t>460000</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>43246</t>
+          <t>55441.88</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>43246</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>0.75</t>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>12195.88</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
@@ -370,12 +370,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/27 15:15:22</t>
+          <t>09/01 11:34:01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>28673</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -397,12 +397,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/27 10:05:01</t>
+          <t>08/27 15:15:22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -412,7 +412,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -424,12 +424,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/20 19:49:17</t>
+          <t>08/27 10:05:01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -439,7 +439,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -451,12 +451,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/20 18:15:36</t>
+          <t>08/20 19:49:17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -466,7 +466,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -478,83 +478,110 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>08/20 18:15:36</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>08/19 13:51:31</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>8333</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>460000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>55441.88</t>
+          <t>460000</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>43246</t>
+          <t>55441.88</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>55441</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>12195.88</t>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0.88</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/01 10:16:07</t>
+          <t>09/01 15:45:01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>11695.91</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/27 14:01:57</t>
+          <t>09/01 10:16:07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21818.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/27 09:56:58</t>
+          <t>08/27 14:01:57</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7142.86</t>
+          <t>21818.18</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/20 18:15:31</t>
+          <t>08/27 09:56:58</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>7142.86</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,166 +243,181 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>08/20 18:15:31</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>5952.38</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>08/19 12:21:27</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>70000</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>8333.33</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/01 11:34:01</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/27 15:15:22</t>
+          <t>09/01 11:34:01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>28673</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -424,12 +439,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/27 10:05:01</t>
+          <t>08/27 15:15:22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -439,7 +454,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -451,12 +466,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/20 19:49:17</t>
+          <t>08/27 10:05:01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -466,7 +481,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -478,12 +493,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/20 18:15:36</t>
+          <t>08/20 19:49:17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -493,7 +508,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -505,83 +520,110 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>08/20 18:15:36</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>08/19 13:51:31</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>8333</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>460000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>55441.88</t>
+          <t>560000</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>55441</t>
+          <t>67137.78</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>55441</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>0.88</t>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>11696.78</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
@@ -412,12 +412,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/01 11:34:01</t>
+          <t>09/01 17:26:18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -439,12 +439,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/27 15:15:22</t>
+          <t>09/01 11:34:01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>28673</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -466,12 +466,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/27 10:05:01</t>
+          <t>08/27 15:15:22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -481,7 +481,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -493,12 +493,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/20 19:49:17</t>
+          <t>08/27 10:05:01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -520,12 +520,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/20 18:15:36</t>
+          <t>08/20 19:49:17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -547,83 +547,110 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>08/20 18:15:36</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>08/19 13:51:31</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>8333</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>560000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>67137.78</t>
+          <t>560000</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>55441</t>
+          <t>67137.78</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>67137</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>11696.78</t>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0.78</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/01 15:45:01</t>
+          <t>09/02 13:48:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11695.91</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/01 10:16:07</t>
+          <t>09/01 15:45:01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>11695.91</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/27 14:01:57</t>
+          <t>09/01 10:16:07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21818.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/27 09:56:58</t>
+          <t>08/27 14:01:57</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7142.86</t>
+          <t>21818.18</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/20 18:15:31</t>
+          <t>08/27 09:56:58</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>7142.86</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,166 +285,181 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>08/20 18:15:31</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>5952.38</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>08/19 12:21:27</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>70000</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>8333.33</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/01 17:26:18</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11696</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/01 11:34:01</t>
+          <t>09/01 17:26:18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -466,12 +481,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/27 15:15:22</t>
+          <t>09/01 11:34:01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>28673</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -493,12 +508,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/27 10:05:01</t>
+          <t>08/27 15:15:22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -508,7 +523,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -520,12 +535,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/20 19:49:17</t>
+          <t>08/27 10:05:01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -535,7 +550,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -547,12 +562,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/20 18:15:36</t>
+          <t>08/20 19:49:17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -562,7 +577,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -574,83 +589,110 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>08/20 18:15:36</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>08/19 13:51:31</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>8333</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>560000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>67137.78</t>
+          <t>660000</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>67137</t>
+          <t>79332.9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>67137</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>0.78</t>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>12195.9</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
@@ -454,12 +454,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/01 17:26:18</t>
+          <t>09/02 15:02:41</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>11696</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -481,12 +481,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/01 11:34:01</t>
+          <t>09/01 17:26:18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -508,12 +508,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/27 15:15:22</t>
+          <t>09/01 11:34:01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>28673</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -535,12 +535,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/27 10:05:01</t>
+          <t>08/27 15:15:22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -562,12 +562,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/20 19:49:17</t>
+          <t>08/27 10:05:01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -589,12 +589,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/20 18:15:36</t>
+          <t>08/20 19:49:17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -616,83 +616,110 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>08/20 18:15:36</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>08/19 13:51:31</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>8333</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>660000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>79332.9</t>
+          <t>660000</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>67137</t>
+          <t>79332.9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>79332</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>12195.9</t>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0.9</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/02 13:48:56</t>
+          <t>09/08 14:59:13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/01 15:45:01</t>
+          <t>09/02 13:48:56</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11695.91</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,7 +159,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/01 10:16:07</t>
+          <t>09/01 15:45:01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>11695.91</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/27 14:01:57</t>
+          <t>09/01 10:16:07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>21818.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/27 09:56:58</t>
+          <t>08/27 14:01:57</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7142.86</t>
+          <t>21818.18</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/20 18:15:31</t>
+          <t>08/27 09:56:58</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>7142.86</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,166 +327,181 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>08/20 18:15:31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>5952.38</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>08/19 12:21:27</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>70000</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>8333.33</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/02 15:02:41</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/01 17:26:18</t>
+          <t>09/02 15:02:41</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11696</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -508,12 +523,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/01 11:34:01</t>
+          <t>09/01 17:26:18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -535,12 +550,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/27 15:15:22</t>
+          <t>09/01 11:34:01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>28673</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -562,12 +577,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/27 10:05:01</t>
+          <t>08/27 15:15:22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -577,7 +592,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -589,12 +604,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/20 19:49:17</t>
+          <t>08/27 10:05:01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -604,7 +619,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -616,12 +631,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/20 18:15:36</t>
+          <t>08/20 19:49:17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -631,7 +646,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -643,83 +658,110 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>08/20 18:15:36</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>08/19 13:51:31</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>8333</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>660000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>79332.9</t>
+          <t>710000</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>79332</t>
+          <t>85285.28</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>79332</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>0.9</t>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>5953.28</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
@@ -496,12 +496,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/02 15:02:41</t>
+          <t>09/08 14:59:19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -523,12 +523,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/01 17:26:18</t>
+          <t>09/02 15:02:41</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11696</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -550,12 +550,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/01 11:34:01</t>
+          <t>09/01 17:26:18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -577,12 +577,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/27 15:15:22</t>
+          <t>09/01 11:34:01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>28673</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -604,12 +604,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/27 10:05:01</t>
+          <t>08/27 15:15:22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -631,12 +631,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/20 19:49:17</t>
+          <t>08/27 10:05:01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -658,12 +658,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/20 18:15:36</t>
+          <t>08/20 19:49:17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -685,83 +685,110 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>08/20 18:15:36</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>08/19 13:51:31</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>8333</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>710000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>85285.28</t>
+          <t>710000</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>79332</t>
+          <t>85285.28</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>79620</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>5953.28</t>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>5665.28</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
@@ -496,12 +496,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/08 14:59:19</t>
+          <t>09/08 19:26:30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -523,12 +523,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/02 15:02:41</t>
+          <t>09/08 14:59:19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -550,12 +550,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/01 17:26:18</t>
+          <t>09/02 15:02:41</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11696</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -577,12 +577,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/01 11:34:01</t>
+          <t>09/01 17:26:18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -604,12 +604,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/27 15:15:22</t>
+          <t>09/01 11:34:01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>28673</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -631,12 +631,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/27 10:05:01</t>
+          <t>08/27 15:15:22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -658,12 +658,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/20 19:49:17</t>
+          <t>08/27 10:05:01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -685,12 +685,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/20 18:15:36</t>
+          <t>08/20 19:49:17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -712,83 +712,110 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>08/20 18:15:36</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>08/19 13:51:31</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>8333</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>710000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>85285.28</t>
+          <t>710000</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>79620</t>
+          <t>85285.28</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>85284</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>5665.28</t>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1.28</t>
         </is>
       </c>
     </row>
